--- a/output/roomself_excel/12841.xlsx
+++ b/output/roomself_excel/12841.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>110111</v>
+        <v>60108</v>
       </c>
       <c r="D2" t="n">
-        <v>2675</v>
+        <v>2091</v>
       </c>
       <c r="E2" t="n">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>266075</v>
+        <v>110111</v>
       </c>
       <c r="D3" t="n">
-        <v>5468</v>
+        <v>2675</v>
       </c>
       <c r="E3" t="n">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68751</v>
+        <v>21841</v>
       </c>
       <c r="D4" t="n">
-        <v>2772</v>
+        <v>1252</v>
       </c>
       <c r="E4" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24669</v>
+        <v>21280</v>
       </c>
       <c r="D5" t="n">
-        <v>1308</v>
+        <v>1168</v>
       </c>
       <c r="E5" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,86 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21280</v>
+        <v>184063</v>
       </c>
       <c r="D6" t="n">
-        <v>1168</v>
+        <v>3444</v>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>68751</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2772</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24669</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>63</v>
+      </c>
+      <c r="D9" t="n">
+        <v>155</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/12841.xlsx
+++ b/output/roomself_excel/12841.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,16 +449,6 @@
           <t>Perimeter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallLength</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallWidth</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -475,12 +465,6 @@
       <c r="D2" t="n">
         <v>2091</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +481,6 @@
       <c r="D3" t="n">
         <v>2675</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +497,6 @@
       <c r="D4" t="n">
         <v>1252</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +513,6 @@
       <c r="D5" t="n">
         <v>1168</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +529,6 @@
       <c r="D6" t="n">
         <v>3444</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +545,6 @@
       <c r="D7" t="n">
         <v>2772</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +561,6 @@
       <c r="D8" t="n">
         <v>1308</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -628,12 +576,6 @@
       </c>
       <c r="D9" t="n">
         <v>155</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/12841.xlsx
+++ b/output/roomself_excel/12841.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
